--- a/data/database_scheduler.xlsx
+++ b/data/database_scheduler.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mersi\BZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9EA0C3B-85B1-42F4-ADE2-98953E7202BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0172E108-5372-4FC6-A018-78E691C320F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
   </bookViews>
   <sheets>
     <sheet name="Guru" sheetId="2" r:id="rId1"/>
@@ -1990,7 +1990,7 @@
         <v>110</v>
       </c>
       <c r="C3" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2001,7 +2001,7 @@
         <v>111</v>
       </c>
       <c r="C4" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2012,7 +2012,7 @@
         <v>112</v>
       </c>
       <c r="C5" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">

--- a/data/database_scheduler.xlsx
+++ b/data/database_scheduler.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mersi\BZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0172E108-5372-4FC6-A018-78E691C320F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00CC911A-B7BF-4EC7-AE02-071F262818B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
   </bookViews>
   <sheets>
     <sheet name="Guru" sheetId="2" r:id="rId1"/>
@@ -2078,7 +2078,7 @@
         <v>109</v>
       </c>
       <c r="C11" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -4844,10 +4844,10 @@
         <v>120</v>
       </c>
       <c r="E121" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F121" s="6">
-        <v>2.2000000000000002</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -4864,10 +4864,10 @@
         <v>128</v>
       </c>
       <c r="E122" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F122" s="6">
-        <v>2.2000000000000002</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -4884,10 +4884,10 @@
         <v>129</v>
       </c>
       <c r="E123" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F123" s="6">
-        <v>2.2000000000000002</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4904,10 +4904,10 @@
         <v>130</v>
       </c>
       <c r="E124" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F124" s="6">
-        <v>2.2000000000000002</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4924,10 +4924,10 @@
         <v>131</v>
       </c>
       <c r="E125" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F125" s="6">
-        <v>2.2000000000000002</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4944,10 +4944,10 @@
         <v>125</v>
       </c>
       <c r="E126" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F126" s="6">
-        <v>2.2000000000000002</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -4964,10 +4964,10 @@
         <v>126</v>
       </c>
       <c r="E127" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F127" s="6">
-        <v>2.2000000000000002</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -4984,10 +4984,10 @@
         <v>127</v>
       </c>
       <c r="E128" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F128" s="6">
-        <v>2.2000000000000002</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -6104,10 +6104,10 @@
         <v>117</v>
       </c>
       <c r="E184" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F184" s="6">
-        <v>2.2000000000000002</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -6124,10 +6124,10 @@
         <v>118</v>
       </c>
       <c r="E185" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F185" s="6">
-        <v>2.2000000000000002</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -6144,10 +6144,10 @@
         <v>121</v>
       </c>
       <c r="E186" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F186" s="6">
-        <v>2.2000000000000002</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -6164,10 +6164,10 @@
         <v>122</v>
       </c>
       <c r="E187" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F187" s="6">
-        <v>2.2000000000000002</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -6184,10 +6184,10 @@
         <v>123</v>
       </c>
       <c r="E188" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F188" s="6">
-        <v>2.2000000000000002</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -6204,10 +6204,10 @@
         <v>119</v>
       </c>
       <c r="E189" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F189" s="6">
-        <v>2.2000000000000002</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -6224,10 +6224,10 @@
         <v>124</v>
       </c>
       <c r="E190" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F190" s="6">
-        <v>2.2000000000000002</v>
+        <v>2.1</v>
       </c>
     </row>
   </sheetData>

--- a/data/database_scheduler.xlsx
+++ b/data/database_scheduler.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mersi\BZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00CC911A-B7BF-4EC7-AE02-071F262818B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14E135A4-034F-4E29-9EC6-BD8ADC52E8F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
   </bookViews>
   <sheets>
     <sheet name="Guru" sheetId="2" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="160">
   <si>
     <t>Nama Guru</t>
   </si>
@@ -474,6 +474,36 @@
   </si>
   <si>
     <t>Pendidikan Agama Kristen</t>
+  </si>
+  <si>
+    <t>Jam_Mulai</t>
+  </si>
+  <si>
+    <t>Jam_Selesai</t>
+  </si>
+  <si>
+    <t>Blok</t>
+  </si>
+  <si>
+    <t>Shift</t>
+  </si>
+  <si>
+    <t>2+2</t>
+  </si>
+  <si>
+    <t>PAGI</t>
+  </si>
+  <si>
+    <t>2+1</t>
+  </si>
+  <si>
+    <t>SIANG</t>
+  </si>
+  <si>
+    <t>2+2+1</t>
+  </si>
+  <si>
+    <t>2+2+2</t>
   </si>
 </sst>
 </file>
@@ -1952,15 +1982,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E91878-6F62-4424-A587-87E66165FF72}">
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.42578125" customWidth="1"/>
     <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="6"/>
+    <col min="5" max="5" width="11.5703125" style="6" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" style="6" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="6"/>
+    <col min="8" max="8" width="15.28515625" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>79</v>
       </c>
@@ -1970,254 +2005,509 @@
       <c r="C1" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>82</v>
       </c>
       <c r="B2" t="s">
         <v>102</v>
       </c>
-      <c r="C2" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C2" s="1">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1">
+        <v>2</v>
+      </c>
+      <c r="E2" s="1">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1">
+        <v>6</v>
+      </c>
+      <c r="G2" s="1">
+        <v>3</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>84</v>
       </c>
       <c r="B3" t="s">
         <v>110</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" s="1">
+        <v>2</v>
+      </c>
+      <c r="E3" s="1">
+        <v>4</v>
+      </c>
+      <c r="F3" s="1">
+        <v>6</v>
+      </c>
+      <c r="G3" s="1">
+        <v>3</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>86</v>
       </c>
       <c r="B4" t="s">
         <v>111</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" s="1">
+        <v>2</v>
+      </c>
+      <c r="E4" s="1">
+        <v>4</v>
+      </c>
+      <c r="F4" s="1">
+        <v>6</v>
+      </c>
+      <c r="G4" s="1">
+        <v>3</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>88</v>
       </c>
       <c r="B5" t="s">
         <v>112</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5" s="1">
+        <v>2</v>
+      </c>
+      <c r="E5" s="1">
+        <v>4</v>
+      </c>
+      <c r="F5" s="1">
+        <v>6</v>
+      </c>
+      <c r="G5" s="1">
+        <v>3</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>89</v>
       </c>
       <c r="B6" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C6" s="1">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1">
+        <v>7</v>
+      </c>
+      <c r="F6" s="1">
+        <v>9</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>90</v>
       </c>
       <c r="B7" t="s">
         <v>85</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7" s="1">
+        <v>2</v>
+      </c>
+      <c r="E7" s="1">
+        <v>3</v>
+      </c>
+      <c r="F7" s="1">
+        <v>4</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>91</v>
       </c>
       <c r="B8" t="s">
         <v>103</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8" s="1">
+        <v>2</v>
+      </c>
+      <c r="E8" s="1">
+        <v>3</v>
+      </c>
+      <c r="F8" s="1">
+        <v>4</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>92</v>
       </c>
       <c r="B9" t="s">
         <v>83</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="6">
+        <v>1</v>
+      </c>
+      <c r="F9" s="6">
+        <v>2</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>93</v>
       </c>
       <c r="B10" t="s">
         <v>108</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="6">
+        <v>1</v>
+      </c>
+      <c r="F10" s="6">
+        <v>2</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>94</v>
       </c>
       <c r="B11" t="s">
         <v>109</v>
       </c>
-      <c r="C11" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C11" s="1">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1">
+        <v>3</v>
+      </c>
+      <c r="E11" s="6">
+        <v>7</v>
+      </c>
+      <c r="F11" s="6">
+        <v>9</v>
+      </c>
+      <c r="G11" s="6">
+        <v>3</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>95</v>
       </c>
       <c r="B12" t="s">
         <v>106</v>
       </c>
-      <c r="C12" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C12" s="1">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="6">
+        <v>1</v>
+      </c>
+      <c r="F12" s="6">
+        <v>3</v>
+      </c>
+      <c r="G12" s="6">
+        <v>3</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>96</v>
       </c>
       <c r="B13" t="s">
         <v>104</v>
       </c>
-      <c r="C13" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C13" s="1">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1">
+        <v>3</v>
+      </c>
+      <c r="E13" s="6">
+        <v>7</v>
+      </c>
+      <c r="F13" s="6">
+        <v>9</v>
+      </c>
+      <c r="G13" s="6">
+        <v>3</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>97</v>
       </c>
       <c r="B14" t="s">
         <v>87</v>
       </c>
-      <c r="C14" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C14" s="1">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1">
+        <v>3</v>
+      </c>
+      <c r="E14" s="6">
+        <v>6</v>
+      </c>
+      <c r="F14" s="6">
+        <v>9</v>
+      </c>
+      <c r="G14" s="6">
+        <v>3</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>98</v>
       </c>
       <c r="B15" t="s">
         <v>113</v>
       </c>
-      <c r="C15" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C15" s="1">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1">
+        <v>3</v>
+      </c>
+      <c r="E15" s="6">
+        <v>7</v>
+      </c>
+      <c r="F15" s="6">
+        <v>9</v>
+      </c>
+      <c r="G15" s="6">
+        <v>3</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>99</v>
       </c>
       <c r="B16" t="s">
         <v>101</v>
       </c>
-      <c r="C16" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C16" s="1">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1">
+        <v>3</v>
+      </c>
+      <c r="E16" s="6">
+        <v>7</v>
+      </c>
+      <c r="F16" s="6">
+        <v>9</v>
+      </c>
+      <c r="G16" s="6">
+        <v>3</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>100</v>
       </c>
       <c r="B17" t="s">
         <v>105</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D17" s="1">
+        <v>3</v>
+      </c>
+      <c r="E17" s="6">
+        <v>8</v>
+      </c>
+      <c r="F17" s="6">
+        <v>9</v>
+      </c>
+      <c r="G17" s="6">
+        <v>1</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
-      <c r="C18" s="3"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C18" s="1"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
-      <c r="C19" s="3"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C19" s="1"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
-      <c r="C20" s="3"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C20" s="1"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
-      <c r="C21" s="3"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C21" s="1"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
-      <c r="C22" s="3"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C22" s="1"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
-      <c r="C23" s="3"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C23" s="1"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
-      <c r="C24" s="3"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C24" s="1"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
-      <c r="C25" s="3"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C25" s="1"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
-      <c r="C26" s="3"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C26" s="1"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
-      <c r="C27" s="3"/>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C27" s="1"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
-      <c r="C28" s="3"/>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C28" s="1"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
-      <c r="C29" s="3"/>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C29" s="1"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
-      <c r="C30" s="3"/>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C30" s="1"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
-      <c r="C31" s="3"/>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C31" s="1"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
-      <c r="C32" s="3"/>
+      <c r="C32" s="1"/>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
-      <c r="C33" s="3"/>
+      <c r="C33" s="1"/>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
-      <c r="C34" s="3"/>
+      <c r="C34" s="1"/>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="3"/>
-      <c r="C35" s="3"/>
+      <c r="C35" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
@@ -2377,7 +2667,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E6B6589-81EB-464C-9D2E-94A0AC6F84FB}">
-  <dimension ref="A1:L190"/>
+  <dimension ref="A1:G190"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.5703125" customWidth="1"/>
@@ -2388,7 +2678,7 @@
     <col min="6" max="6" width="10.85546875" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>39</v>
       </c>
@@ -2408,13 +2698,8 @@
         <v>133</v>
       </c>
       <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>43</v>
       </c>
@@ -2434,13 +2719,8 @@
         <v>134</v>
       </c>
       <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>43</v>
       </c>
@@ -2460,13 +2740,8 @@
         <v>134</v>
       </c>
       <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>43</v>
       </c>
@@ -2486,13 +2761,8 @@
         <v>134</v>
       </c>
       <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>43</v>
       </c>
@@ -2512,13 +2782,8 @@
         <v>134</v>
       </c>
       <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>43</v>
       </c>
@@ -2538,13 +2803,8 @@
         <v>134</v>
       </c>
       <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>45</v>
       </c>
@@ -2564,13 +2824,8 @@
         <v>3</v>
       </c>
       <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>45</v>
       </c>
@@ -2590,7 +2845,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>45</v>
       </c>
@@ -2610,7 +2865,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>45</v>
       </c>
@@ -2630,7 +2885,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>45</v>
       </c>
@@ -2650,7 +2905,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>47</v>
       </c>
@@ -2670,7 +2925,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>47</v>
       </c>
@@ -2690,7 +2945,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>47</v>
       </c>
@@ -2710,7 +2965,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>47</v>
       </c>
@@ -2730,7 +2985,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>47</v>
       </c>

--- a/data/database_scheduler.xlsx
+++ b/data/database_scheduler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mersi\BZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14E135A4-034F-4E29-9EC6-BD8ADC52E8F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7816213D-11AC-4845-A56D-C88C1C2A38B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
   </bookViews>
@@ -2168,7 +2168,7 @@
         <v>3</v>
       </c>
       <c r="F7" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>158</v>
@@ -2194,7 +2194,7 @@
         <v>3</v>
       </c>
       <c r="F8" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>154</v>
@@ -2220,7 +2220,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>158</v>
@@ -2298,7 +2298,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G12" s="6">
         <v>3</v>

--- a/data/database_scheduler.xlsx
+++ b/data/database_scheduler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mersi\BZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7816213D-11AC-4845-A56D-C88C1C2A38B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A59EA6E6-A10A-4865-8944-C078F0517503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="159">
   <si>
     <t>Nama Guru</t>
   </si>
@@ -501,9 +501,6 @@
   </si>
   <si>
     <t>2+2+1</t>
-  </si>
-  <si>
-    <t>2+2+2</t>
   </si>
 </sst>
 </file>
@@ -2249,7 +2246,7 @@
         <v>2</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>155</v>

--- a/data/database_scheduler.xlsx
+++ b/data/database_scheduler.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mersi\BZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A59EA6E6-A10A-4865-8944-C078F0517503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CF94233-1232-4811-8D71-A5395196C5B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
   </bookViews>
   <sheets>
     <sheet name="Guru" sheetId="2" r:id="rId1"/>
@@ -2260,13 +2260,13 @@
         <v>109</v>
       </c>
       <c r="C11" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F11" s="6">
         <v>9</v>
@@ -2390,19 +2390,19 @@
         <v>101</v>
       </c>
       <c r="C16" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" s="1">
         <v>3</v>
       </c>
       <c r="E16" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F16" s="6">
         <v>9</v>
       </c>
       <c r="G16" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>157</v>

--- a/data/database_scheduler.xlsx
+++ b/data/database_scheduler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mersi\BZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CF94233-1232-4811-8D71-A5395196C5B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5408762E-9247-42CD-B20E-6FF570E5AF3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="160">
   <si>
     <t>Nama Guru</t>
   </si>
@@ -501,6 +501,9 @@
   </si>
   <si>
     <t>2+2+1</t>
+  </si>
+  <si>
+    <t>Milenia, S.Pd.</t>
   </si>
 </sst>
 </file>
@@ -3536,10 +3539,10 @@
         <v>117</v>
       </c>
       <c r="E43" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F43" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -3556,10 +3559,10 @@
         <v>118</v>
       </c>
       <c r="E44" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F44" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -3576,10 +3579,10 @@
         <v>121</v>
       </c>
       <c r="E45" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F45" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -3596,10 +3599,10 @@
         <v>122</v>
       </c>
       <c r="E46" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F46" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -3616,10 +3619,10 @@
         <v>123</v>
       </c>
       <c r="E47" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F47" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -3636,10 +3639,10 @@
         <v>119</v>
       </c>
       <c r="E48" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F48" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -3656,10 +3659,10 @@
         <v>124</v>
       </c>
       <c r="E49" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F49" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -3676,10 +3679,10 @@
         <v>120</v>
       </c>
       <c r="E50" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F50" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -3696,10 +3699,10 @@
         <v>128</v>
       </c>
       <c r="E51" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F51" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -3716,10 +3719,10 @@
         <v>129</v>
       </c>
       <c r="E52" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F52" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -3736,10 +3739,10 @@
         <v>130</v>
       </c>
       <c r="E53" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F53" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -3756,10 +3759,10 @@
         <v>131</v>
       </c>
       <c r="E54" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F54" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -5096,10 +5099,10 @@
         <v>120</v>
       </c>
       <c r="E121" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F121" s="6">
-        <v>2.1</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -5116,10 +5119,10 @@
         <v>128</v>
       </c>
       <c r="E122" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F122" s="6">
-        <v>2.1</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -5136,10 +5139,10 @@
         <v>129</v>
       </c>
       <c r="E123" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F123" s="6">
-        <v>2.1</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -5156,10 +5159,10 @@
         <v>130</v>
       </c>
       <c r="E124" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F124" s="6">
-        <v>2.1</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -5176,10 +5179,10 @@
         <v>131</v>
       </c>
       <c r="E125" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F125" s="6">
-        <v>2.1</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -5196,10 +5199,10 @@
         <v>125</v>
       </c>
       <c r="E126" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F126" s="6">
-        <v>2.1</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -5216,10 +5219,10 @@
         <v>126</v>
       </c>
       <c r="E127" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F127" s="6">
-        <v>2.1</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -5236,10 +5239,10 @@
         <v>127</v>
       </c>
       <c r="E128" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F128" s="6">
-        <v>2.1</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -6207,7 +6210,7 @@
         <v>75</v>
       </c>
       <c r="B177" t="s">
-        <v>36</v>
+        <v>159</v>
       </c>
       <c r="C177" t="s">
         <v>85</v>
@@ -6227,7 +6230,7 @@
         <v>75</v>
       </c>
       <c r="B178" t="s">
-        <v>36</v>
+        <v>159</v>
       </c>
       <c r="C178" t="s">
         <v>85</v>
@@ -6247,7 +6250,7 @@
         <v>75</v>
       </c>
       <c r="B179" t="s">
-        <v>36</v>
+        <v>159</v>
       </c>
       <c r="C179" t="s">
         <v>85</v>
@@ -6267,7 +6270,7 @@
         <v>75</v>
       </c>
       <c r="B180" t="s">
-        <v>36</v>
+        <v>159</v>
       </c>
       <c r="C180" t="s">
         <v>85</v>
@@ -6287,7 +6290,7 @@
         <v>75</v>
       </c>
       <c r="B181" t="s">
-        <v>36</v>
+        <v>159</v>
       </c>
       <c r="C181" t="s">
         <v>85</v>
@@ -6356,10 +6359,10 @@
         <v>117</v>
       </c>
       <c r="E184" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F184" s="6">
-        <v>2.1</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -6376,10 +6379,10 @@
         <v>118</v>
       </c>
       <c r="E185" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F185" s="6">
-        <v>2.1</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -6396,10 +6399,10 @@
         <v>121</v>
       </c>
       <c r="E186" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F186" s="6">
-        <v>2.1</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -6416,10 +6419,10 @@
         <v>122</v>
       </c>
       <c r="E187" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F187" s="6">
-        <v>2.1</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -6436,10 +6439,10 @@
         <v>123</v>
       </c>
       <c r="E188" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F188" s="6">
-        <v>2.1</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -6456,10 +6459,10 @@
         <v>119</v>
       </c>
       <c r="E189" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F189" s="6">
-        <v>2.1</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -6476,10 +6479,10 @@
         <v>124</v>
       </c>
       <c r="E190" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F190" s="6">
-        <v>2.1</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
   </sheetData>

--- a/data/database_scheduler.xlsx
+++ b/data/database_scheduler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mersi\BZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5408762E-9247-42CD-B20E-6FF570E5AF3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58533851-303D-41C8-AF94-8604B6B3720B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
   </bookViews>
@@ -2269,13 +2269,13 @@
         <v>2</v>
       </c>
       <c r="E11" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F11" s="6">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G11" s="6">
-        <v>3</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>157</v>

--- a/data/database_scheduler.xlsx
+++ b/data/database_scheduler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mersi\BZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58533851-303D-41C8-AF94-8604B6B3720B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F670461D-1D8C-412C-8FC2-C7081D0B83C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
   </bookViews>
@@ -1747,7 +1747,7 @@
         <v>4</v>
       </c>
       <c r="E22" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -1968,7 +1968,7 @@
         <v>4</v>
       </c>
       <c r="E35" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -5679,10 +5679,10 @@
         <v>125</v>
       </c>
       <c r="E150" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F150" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -5699,10 +5699,10 @@
         <v>126</v>
       </c>
       <c r="E151" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F151" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -5719,10 +5719,10 @@
         <v>127</v>
       </c>
       <c r="E152" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F152" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">

--- a/data/database_scheduler.xlsx
+++ b/data/database_scheduler.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mersi\BZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F670461D-1D8C-412C-8FC2-C7081D0B83C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31ADEC0D-6820-4D82-A93E-8806A4537D7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
   </bookViews>
   <sheets>
     <sheet name="Guru" sheetId="2" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="159">
   <si>
     <t>Nama Guru</t>
   </si>
@@ -132,9 +132,6 @@
   </si>
   <si>
     <t>Anisa Safera Proborini, S.Pd.</t>
-  </si>
-  <si>
-    <t>Krisma Dewi, S.Pd.</t>
   </si>
   <si>
     <t>Anggi Supriyadi, S.Hum</t>
@@ -1378,30 +1375,30 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
         <v>2</v>
@@ -1412,13 +1409,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
         <v>4</v>
@@ -1429,13 +1426,13 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
         <v>6</v>
@@ -1446,13 +1443,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
         <v>8</v>
@@ -1463,13 +1460,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
         <v>6</v>
@@ -1480,13 +1477,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
         <v>4</v>
@@ -1497,13 +1494,13 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
         <v>8</v>
@@ -1514,13 +1511,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
         <v>6</v>
@@ -1531,13 +1528,13 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
         <v>8</v>
@@ -1548,13 +1545,13 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
         <v>6</v>
@@ -1565,13 +1562,13 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B12" t="s">
         <v>15</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D12" t="s">
         <v>4</v>
@@ -1582,13 +1579,13 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B13" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s">
         <v>4</v>
@@ -1599,13 +1596,13 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B14" t="s">
         <v>17</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D14" t="s">
         <v>6</v>
@@ -1616,13 +1613,13 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B15" t="s">
         <v>18</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D15" t="s">
         <v>4</v>
@@ -1633,13 +1630,13 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B16" t="s">
         <v>19</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" t="s">
         <v>20</v>
@@ -1650,13 +1647,13 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B17" t="s">
         <v>21</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D17" t="s">
         <v>4</v>
@@ -1667,13 +1664,13 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B18" t="s">
         <v>22</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D18" t="s">
         <v>8</v>
@@ -1684,13 +1681,13 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B19" t="s">
         <v>23</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D19" t="s">
         <v>8</v>
@@ -1701,13 +1698,13 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B20" t="s">
         <v>24</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D20" t="s">
         <v>2</v>
@@ -1718,13 +1715,13 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B21" t="s">
         <v>25</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D21" t="s">
         <v>8</v>
@@ -1735,13 +1732,13 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B22" t="s">
         <v>26</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D22" t="s">
         <v>4</v>
@@ -1752,13 +1749,13 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B23" t="s">
         <v>27</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D23" t="s">
         <v>4</v>
@@ -1769,13 +1766,13 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B24" t="s">
         <v>28</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D24" t="s">
         <v>2</v>
@@ -1786,13 +1783,13 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B25" t="s">
         <v>29</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D25" t="s">
         <v>2</v>
@@ -1803,13 +1800,13 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B26" t="s">
         <v>30</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D26" t="s">
         <v>20</v>
@@ -1820,13 +1817,13 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B27" t="s">
         <v>31</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D27" t="s">
         <v>20</v>
@@ -1837,13 +1834,13 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B28" t="s">
         <v>31</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D28" t="s">
         <v>6</v>
@@ -1854,13 +1851,13 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B29" t="s">
         <v>32</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D29" t="s">
         <v>4</v>
@@ -1871,13 +1868,13 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B30" t="s">
         <v>33</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D30" t="s">
         <v>8</v>
@@ -1888,13 +1885,13 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B31" t="s">
         <v>34</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D31" t="s">
         <v>6</v>
@@ -1905,13 +1902,13 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B32" t="s">
         <v>35</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D32" t="s">
         <v>2</v>
@@ -1922,13 +1919,13 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>158</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D33" t="s">
         <v>6</v>
@@ -1939,13 +1936,13 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D34" t="s">
         <v>4</v>
@@ -1956,13 +1953,13 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B35" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="B35" t="s">
-        <v>38</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>78</v>
       </c>
       <c r="D35" t="s">
         <v>4</v>
@@ -1997,36 +1994,36 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="D1" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C2" s="1">
         <v>3</v>
@@ -2044,15 +2041,15 @@
         <v>3</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C3" s="1">
         <v>0</v>
@@ -2070,15 +2067,15 @@
         <v>3</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C4" s="1">
         <v>0</v>
@@ -2096,15 +2093,15 @@
         <v>3</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C5" s="1">
         <v>0</v>
@@ -2122,15 +2119,15 @@
         <v>3</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C6" s="1">
         <v>3</v>
@@ -2145,18 +2142,18 @@
         <v>9</v>
       </c>
       <c r="G6" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C7" s="1">
         <v>6</v>
@@ -2171,18 +2168,18 @@
         <v>6</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C8" s="1">
         <v>4</v>
@@ -2197,18 +2194,18 @@
         <v>6</v>
       </c>
       <c r="G8" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C9" s="1">
         <v>5</v>
@@ -2223,18 +2220,18 @@
         <v>4</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C10" s="1">
         <v>5</v>
@@ -2249,18 +2246,18 @@
         <v>2</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C11" s="1">
         <v>4</v>
@@ -2278,15 +2275,15 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C12" s="1">
         <v>3</v>
@@ -2304,15 +2301,15 @@
         <v>3</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C13" s="1">
         <v>3</v>
@@ -2330,15 +2327,15 @@
         <v>3</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C14" s="1">
         <v>3</v>
@@ -2356,15 +2353,15 @@
         <v>3</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C15" s="1">
         <v>3</v>
@@ -2382,15 +2379,15 @@
         <v>3</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C16" s="1">
         <v>2</v>
@@ -2408,15 +2405,15 @@
         <v>2</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C17" s="1">
         <v>0</v>
@@ -2434,7 +2431,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -2527,18 +2524,18 @@
   <sheetData>
     <row r="1" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B2" s="3">
         <v>7</v>
@@ -2547,7 +2544,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B3" s="3">
         <v>7</v>
@@ -2556,7 +2553,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B4" s="3">
         <v>7</v>
@@ -2565,7 +2562,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B5" s="3">
         <v>7</v>
@@ -2574,7 +2571,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B6" s="3">
         <v>7</v>
@@ -2582,7 +2579,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B7" s="3">
         <v>8</v>
@@ -2590,7 +2587,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B8" s="3">
         <v>8</v>
@@ -2598,7 +2595,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B9" s="3">
         <v>8</v>
@@ -2606,7 +2603,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
@@ -2614,7 +2611,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
@@ -2622,7 +2619,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B12" s="3">
         <v>9</v>
@@ -2630,7 +2627,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B13" s="3">
         <v>9</v>
@@ -2638,7 +2635,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B14" s="3">
         <v>9</v>
@@ -2646,7 +2643,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B15" s="3">
         <v>9</v>
@@ -2654,7 +2651,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B16" s="3">
         <v>9</v>
@@ -2680,142 +2677,142 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>133</v>
       </c>
       <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E2" s="6">
         <v>5</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G2" s="3"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E3" s="6">
         <v>5</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G3" s="3"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E4" s="6">
         <v>5</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G4" s="3"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B5" t="s">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E5" s="6">
         <v>5</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E6" s="6">
         <v>5</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G6" s="3"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E7" s="6">
         <v>3</v>
@@ -2827,16 +2824,16 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E8" s="6">
         <v>3</v>
@@ -2847,16 +2844,16 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E9" s="6">
         <v>3</v>
@@ -2867,16 +2864,16 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E10" s="6">
         <v>3</v>
@@ -2887,16 +2884,16 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E11" s="6">
         <v>3</v>
@@ -2907,16 +2904,16 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B12" t="s">
         <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E12" s="6">
         <v>4</v>
@@ -2927,16 +2924,16 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B13" t="s">
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E13" s="6">
         <v>4</v>
@@ -2947,16 +2944,16 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B14" t="s">
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D14" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E14" s="6">
         <v>4</v>
@@ -2967,16 +2964,16 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B15" t="s">
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E15" s="6">
         <v>4</v>
@@ -2987,16 +2984,16 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B16" t="s">
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D16" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E16" s="6">
         <v>4</v>
@@ -3007,116 +3004,116 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B17" t="s">
         <v>7</v>
       </c>
       <c r="C17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E17" s="6">
         <v>5</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B18" t="s">
         <v>7</v>
       </c>
       <c r="C18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E18" s="6">
         <v>5</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B19" t="s">
         <v>7</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D19" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E19" s="6">
         <v>5</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B20" t="s">
         <v>7</v>
       </c>
       <c r="C20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D20" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E20" s="6">
         <v>5</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B21" t="s">
         <v>7</v>
       </c>
       <c r="C21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D21" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E21" s="6">
         <v>5</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B22" t="s">
         <v>9</v>
       </c>
       <c r="C22" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E22" s="6">
         <v>4</v>
@@ -3127,16 +3124,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B23" t="s">
         <v>9</v>
       </c>
       <c r="C23" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E23" s="6">
         <v>4</v>
@@ -3147,16 +3144,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B24" t="s">
         <v>9</v>
       </c>
       <c r="C24" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D24" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E24" s="6">
         <v>4</v>
@@ -3167,16 +3164,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B25" t="s">
         <v>9</v>
       </c>
       <c r="C25" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D25" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E25" s="6">
         <v>4</v>
@@ -3187,16 +3184,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B26" t="s">
         <v>9</v>
       </c>
       <c r="C26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D26" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E26" s="6">
         <v>4</v>
@@ -3207,16 +3204,16 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B27" t="s">
         <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D27" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E27" s="6">
         <v>3</v>
@@ -3227,16 +3224,16 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B28" t="s">
         <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D28" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E28" s="6">
         <v>3</v>
@@ -3247,16 +3244,16 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B29" t="s">
         <v>10</v>
       </c>
       <c r="C29" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D29" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E29" s="6">
         <v>3</v>
@@ -3267,16 +3264,16 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B30" t="s">
         <v>10</v>
       </c>
       <c r="C30" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D30" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E30" s="6">
         <v>3</v>
@@ -3287,16 +3284,16 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B31" t="s">
         <v>10</v>
       </c>
       <c r="C31" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D31" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E31" s="6">
         <v>3</v>
@@ -3307,16 +3304,16 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B32" t="s">
         <v>10</v>
       </c>
       <c r="C32" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D32" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E32" s="6">
         <v>3</v>
@@ -3327,16 +3324,16 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B33" t="s">
         <v>10</v>
       </c>
       <c r="C33" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D33" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E33" s="6">
         <v>3</v>
@@ -3347,16 +3344,16 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B34" t="s">
         <v>10</v>
       </c>
       <c r="C34" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D34" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E34" s="6">
         <v>3</v>
@@ -3367,16 +3364,16 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B35" t="s">
         <v>11</v>
       </c>
       <c r="C35" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D35" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E35" s="6">
         <v>3</v>
@@ -3387,16 +3384,16 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B36" t="s">
         <v>11</v>
       </c>
       <c r="C36" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D36" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E36" s="6">
         <v>3</v>
@@ -3407,16 +3404,16 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B37" t="s">
         <v>11</v>
       </c>
       <c r="C37" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D37" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E37" s="6">
         <v>3</v>
@@ -3427,16 +3424,16 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B38" t="s">
         <v>11</v>
       </c>
       <c r="C38" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D38" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E38" s="6">
         <v>3</v>
@@ -3447,16 +3444,16 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B39" t="s">
         <v>11</v>
       </c>
       <c r="C39" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D39" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E39" s="6">
         <v>3</v>
@@ -3467,16 +3464,16 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B40" t="s">
         <v>11</v>
       </c>
       <c r="C40" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D40" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E40" s="6">
         <v>3</v>
@@ -3487,16 +3484,16 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B41" t="s">
         <v>11</v>
       </c>
       <c r="C41" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D41" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E41" s="6">
         <v>3</v>
@@ -3507,16 +3504,16 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B42" t="s">
         <v>11</v>
       </c>
       <c r="C42" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D42" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E42" s="6">
         <v>3</v>
@@ -3527,16 +3524,16 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B43" t="s">
         <v>12</v>
       </c>
       <c r="C43" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D43" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E43" s="6">
         <v>2</v>
@@ -3547,16 +3544,16 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B44" t="s">
         <v>12</v>
       </c>
       <c r="C44" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D44" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E44" s="6">
         <v>2</v>
@@ -3567,16 +3564,16 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B45" t="s">
         <v>12</v>
       </c>
       <c r="C45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D45" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E45" s="6">
         <v>2</v>
@@ -3587,16 +3584,16 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B46" t="s">
         <v>12</v>
       </c>
       <c r="C46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D46" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E46" s="6">
         <v>2</v>
@@ -3607,16 +3604,16 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B47" t="s">
         <v>12</v>
       </c>
       <c r="C47" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D47" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E47" s="6">
         <v>2</v>
@@ -3627,16 +3624,16 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B48" t="s">
         <v>12</v>
       </c>
       <c r="C48" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D48" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E48" s="6">
         <v>2</v>
@@ -3647,16 +3644,16 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B49" t="s">
         <v>12</v>
       </c>
       <c r="C49" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D49" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E49" s="6">
         <v>2</v>
@@ -3667,16 +3664,16 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B50" t="s">
         <v>12</v>
       </c>
       <c r="C50" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D50" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E50" s="6">
         <v>2</v>
@@ -3687,16 +3684,16 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B51" t="s">
         <v>12</v>
       </c>
       <c r="C51" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D51" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E51" s="6">
         <v>2</v>
@@ -3707,16 +3704,16 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B52" t="s">
         <v>12</v>
       </c>
       <c r="C52" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D52" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E52" s="6">
         <v>2</v>
@@ -3727,16 +3724,16 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B53" t="s">
         <v>12</v>
       </c>
       <c r="C53" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D53" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E53" s="6">
         <v>2</v>
@@ -3747,16 +3744,16 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B54" t="s">
         <v>12</v>
       </c>
       <c r="C54" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D54" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E54" s="6">
         <v>2</v>
@@ -3767,16 +3764,16 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
       </c>
       <c r="C55" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D55" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E55" s="6">
         <v>3</v>
@@ -3787,16 +3784,16 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
       </c>
       <c r="C56" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D56" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E56" s="6">
         <v>3</v>
@@ -3807,16 +3804,16 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B57" t="s">
         <v>13</v>
       </c>
       <c r="C57" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D57" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E57" s="6">
         <v>3</v>
@@ -3827,16 +3824,16 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
       </c>
       <c r="C58" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D58" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E58" s="6">
         <v>3</v>
@@ -3847,16 +3844,16 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
       </c>
       <c r="C59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D59" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E59" s="6">
         <v>3</v>
@@ -3867,116 +3864,116 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B60" t="s">
         <v>14</v>
       </c>
       <c r="C60" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D60" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E60" s="6">
         <v>6</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B61" t="s">
         <v>14</v>
       </c>
       <c r="C61" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D61" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E61" s="6">
         <v>6</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B62" t="s">
         <v>14</v>
       </c>
       <c r="C62" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D62" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E62" s="6">
         <v>6</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B63" t="s">
         <v>14</v>
       </c>
       <c r="C63" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D63" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E63" s="6">
         <v>6</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B64" t="s">
         <v>14</v>
       </c>
       <c r="C64" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D64" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E64" s="6">
         <v>6</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B65" t="s">
         <v>15</v>
       </c>
       <c r="C65" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D65" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E65" s="6">
         <v>0</v>
@@ -3987,16 +3984,16 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B66" t="s">
         <v>15</v>
       </c>
       <c r="C66" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D66" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E66" s="6">
         <v>0</v>
@@ -4007,16 +4004,16 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B67" t="s">
         <v>15</v>
       </c>
       <c r="C67" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D67" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E67" s="6">
         <v>0</v>
@@ -4027,16 +4024,16 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B68" t="s">
         <v>15</v>
       </c>
       <c r="C68" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D68" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E68" s="6">
         <v>0</v>
@@ -4047,16 +4044,16 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B69" t="s">
         <v>15</v>
       </c>
       <c r="C69" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D69" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E69" s="6">
         <v>0</v>
@@ -4067,16 +4064,16 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B70" t="s">
         <v>16</v>
       </c>
       <c r="C70" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D70" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E70" s="6">
         <v>0</v>
@@ -4087,16 +4084,16 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B71" t="s">
         <v>16</v>
       </c>
       <c r="C71" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D71" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E71" s="6">
         <v>0</v>
@@ -4107,16 +4104,16 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B72" t="s">
         <v>16</v>
       </c>
       <c r="C72" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D72" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E72" s="6">
         <v>0</v>
@@ -4127,16 +4124,16 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B73" t="s">
         <v>16</v>
       </c>
       <c r="C73" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D73" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E73" s="6">
         <v>0</v>
@@ -4147,16 +4144,16 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B74" t="s">
         <v>16</v>
       </c>
       <c r="C74" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D74" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E74" s="6">
         <v>0</v>
@@ -4167,116 +4164,116 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B75" t="s">
         <v>17</v>
       </c>
       <c r="C75" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D75" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E75" s="6">
         <v>6</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B76" t="s">
         <v>17</v>
       </c>
       <c r="C76" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D76" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E76" s="6">
         <v>6</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B77" t="s">
         <v>17</v>
       </c>
       <c r="C77" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D77" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E77" s="6">
         <v>6</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B78" t="s">
         <v>17</v>
       </c>
       <c r="C78" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D78" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E78" s="6">
         <v>6</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B79" t="s">
         <v>17</v>
       </c>
       <c r="C79" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D79" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E79" s="6">
         <v>6</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B80" t="s">
         <v>18</v>
       </c>
       <c r="C80" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D80" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E80" s="6">
         <v>3</v>
@@ -4287,16 +4284,16 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B81" t="s">
         <v>18</v>
       </c>
       <c r="C81" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D81" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E81" s="6">
         <v>3</v>
@@ -4307,16 +4304,16 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B82" t="s">
         <v>18</v>
       </c>
       <c r="C82" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D82" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E82" s="6">
         <v>3</v>
@@ -4327,16 +4324,16 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B83" t="s">
         <v>18</v>
       </c>
       <c r="C83" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D83" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E83" s="6">
         <v>3</v>
@@ -4347,16 +4344,16 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B84" t="s">
         <v>18</v>
       </c>
       <c r="C84" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D84" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E84" s="6">
         <v>3</v>
@@ -4367,16 +4364,16 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B85" t="s">
         <v>18</v>
       </c>
       <c r="C85" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D85" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E85" s="6">
         <v>3</v>
@@ -4387,16 +4384,16 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B86" t="s">
         <v>18</v>
       </c>
       <c r="C86" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D86" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E86" s="6">
         <v>3</v>
@@ -4407,16 +4404,16 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B87" t="s">
         <v>18</v>
       </c>
       <c r="C87" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D87" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E87" s="6">
         <v>3</v>
@@ -4427,16 +4424,16 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B88" t="s">
         <v>19</v>
       </c>
       <c r="C88" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D88" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E88" s="6">
         <v>3</v>
@@ -4447,16 +4444,16 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B89" t="s">
         <v>19</v>
       </c>
       <c r="C89" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D89" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E89" s="6">
         <v>3</v>
@@ -4467,16 +4464,16 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B90" t="s">
         <v>19</v>
       </c>
       <c r="C90" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D90" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E90" s="6">
         <v>3</v>
@@ -4487,16 +4484,16 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B91" t="s">
         <v>19</v>
       </c>
       <c r="C91" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D91" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E91" s="6">
         <v>3</v>
@@ -4507,16 +4504,16 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B92" t="s">
         <v>19</v>
       </c>
       <c r="C92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D92" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E92" s="6">
         <v>3</v>
@@ -4527,16 +4524,16 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B93" t="s">
         <v>19</v>
       </c>
       <c r="C93" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D93" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E93" s="6">
         <v>3</v>
@@ -4547,16 +4544,16 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B94" t="s">
         <v>19</v>
       </c>
       <c r="C94" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D94" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E94" s="6">
         <v>3</v>
@@ -4567,16 +4564,16 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B95" t="s">
         <v>19</v>
       </c>
       <c r="C95" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D95" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E95" s="6">
         <v>3</v>
@@ -4587,16 +4584,16 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B96" t="s">
         <v>21</v>
       </c>
       <c r="C96" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D96" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E96" s="6">
         <v>0</v>
@@ -4607,16 +4604,16 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B97" t="s">
         <v>21</v>
       </c>
       <c r="C97" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D97" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E97" s="6">
         <v>0</v>
@@ -4627,16 +4624,16 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B98" t="s">
         <v>21</v>
       </c>
       <c r="C98" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D98" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E98" s="6">
         <v>0</v>
@@ -4647,16 +4644,16 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B99" t="s">
         <v>21</v>
       </c>
       <c r="C99" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D99" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E99" s="6">
         <v>0</v>
@@ -4667,16 +4664,16 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B100" t="s">
         <v>21</v>
       </c>
       <c r="C100" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D100" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E100" s="6">
         <v>0</v>
@@ -4687,16 +4684,16 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B101" t="s">
         <v>22</v>
       </c>
       <c r="C101" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D101" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E101" s="6">
         <v>3</v>
@@ -4707,16 +4704,16 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B102" t="s">
         <v>22</v>
       </c>
       <c r="C102" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D102" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E102" s="6">
         <v>3</v>
@@ -4727,16 +4724,16 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B103" t="s">
         <v>22</v>
       </c>
       <c r="C103" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D103" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E103" s="6">
         <v>3</v>
@@ -4747,16 +4744,16 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B104" t="s">
         <v>22</v>
       </c>
       <c r="C104" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D104" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E104" s="6">
         <v>3</v>
@@ -4767,16 +4764,16 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B105" t="s">
         <v>22</v>
       </c>
       <c r="C105" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D105" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E105" s="6">
         <v>3</v>
@@ -4787,316 +4784,316 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B106" t="s">
         <v>23</v>
       </c>
       <c r="C106" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D106" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E106" s="6">
         <v>5</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B107" t="s">
         <v>23</v>
       </c>
       <c r="C107" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D107" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E107" s="6">
         <v>5</v>
       </c>
       <c r="F107" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B108" t="s">
         <v>23</v>
       </c>
       <c r="C108" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D108" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E108" s="6">
         <v>5</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B109" t="s">
         <v>23</v>
       </c>
       <c r="C109" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D109" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E109" s="6">
         <v>5</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B110" t="s">
         <v>23</v>
       </c>
       <c r="C110" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D110" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E110" s="6">
         <v>5</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B111" t="s">
         <v>24</v>
       </c>
       <c r="C111" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D111" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E111" s="6">
         <v>5</v>
       </c>
       <c r="F111" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B112" t="s">
         <v>24</v>
       </c>
       <c r="C112" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D112" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E112" s="6">
         <v>5</v>
       </c>
       <c r="F112" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B113" t="s">
         <v>24</v>
       </c>
       <c r="C113" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D113" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E113" s="6">
         <v>5</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B114" t="s">
         <v>24</v>
       </c>
       <c r="C114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D114" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E114" s="6">
         <v>5</v>
       </c>
       <c r="F114" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B115" t="s">
         <v>24</v>
       </c>
       <c r="C115" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D115" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E115" s="6">
         <v>5</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B116" t="s">
         <v>25</v>
       </c>
       <c r="C116" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D116" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E116" s="6">
         <v>5</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B117" t="s">
         <v>25</v>
       </c>
       <c r="C117" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D117" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E117" s="6">
         <v>5</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B118" t="s">
         <v>25</v>
       </c>
       <c r="C118" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D118" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E118" s="6">
         <v>5</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B119" t="s">
         <v>25</v>
       </c>
       <c r="C119" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D119" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E119" s="6">
         <v>5</v>
       </c>
       <c r="F119" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B120" t="s">
         <v>25</v>
       </c>
       <c r="C120" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D120" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E120" s="6">
         <v>5</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B121" t="s">
         <v>26</v>
       </c>
       <c r="C121" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D121" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E121" s="6">
         <v>4</v>
@@ -5107,16 +5104,16 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B122" t="s">
         <v>26</v>
       </c>
       <c r="C122" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D122" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E122" s="6">
         <v>4</v>
@@ -5127,16 +5124,16 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B123" t="s">
         <v>26</v>
       </c>
       <c r="C123" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D123" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E123" s="6">
         <v>4</v>
@@ -5147,16 +5144,16 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B124" t="s">
         <v>26</v>
       </c>
       <c r="C124" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D124" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E124" s="6">
         <v>4</v>
@@ -5167,16 +5164,16 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B125" t="s">
         <v>26</v>
       </c>
       <c r="C125" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D125" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E125" s="6">
         <v>4</v>
@@ -5187,16 +5184,16 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B126" t="s">
         <v>26</v>
       </c>
       <c r="C126" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D126" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E126" s="6">
         <v>4</v>
@@ -5207,16 +5204,16 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B127" t="s">
         <v>26</v>
       </c>
       <c r="C127" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D127" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E127" s="6">
         <v>4</v>
@@ -5227,16 +5224,16 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B128" t="s">
         <v>26</v>
       </c>
       <c r="C128" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D128" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E128" s="6">
         <v>4</v>
@@ -5247,16 +5244,16 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B129" t="s">
         <v>27</v>
       </c>
       <c r="C129" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D129" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E129" s="6">
         <v>0</v>
@@ -5267,16 +5264,16 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B130" t="s">
         <v>27</v>
       </c>
       <c r="C130" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D130" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E130" s="6">
         <v>0</v>
@@ -5287,16 +5284,16 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B131" t="s">
         <v>27</v>
       </c>
       <c r="C131" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D131" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E131" s="6">
         <v>0</v>
@@ -5307,16 +5304,16 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B132" t="s">
         <v>28</v>
       </c>
       <c r="C132" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D132" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E132" s="6">
         <v>0</v>
@@ -5327,16 +5324,16 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B133" t="s">
         <v>28</v>
       </c>
       <c r="C133" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D133" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E133" s="6">
         <v>0</v>
@@ -5347,16 +5344,16 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B134" t="s">
         <v>28</v>
       </c>
       <c r="C134" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D134" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E134" s="6">
         <v>0</v>
@@ -5367,16 +5364,16 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B135" t="s">
         <v>29</v>
       </c>
       <c r="C135" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D135" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E135" s="6">
         <v>0</v>
@@ -5387,16 +5384,16 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B136" t="s">
         <v>29</v>
       </c>
       <c r="C136" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D136" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E136" s="6">
         <v>0</v>
@@ -5407,16 +5404,16 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B137" t="s">
         <v>29</v>
       </c>
       <c r="C137" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D137" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E137" s="6">
         <v>0</v>
@@ -5427,16 +5424,16 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B138" t="s">
         <v>30</v>
       </c>
       <c r="C138" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D138" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E138" s="6">
         <v>3</v>
@@ -5447,16 +5444,16 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B139" t="s">
         <v>30</v>
       </c>
       <c r="C139" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D139" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E139" s="6">
         <v>3</v>
@@ -5467,16 +5464,16 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B140" t="s">
         <v>30</v>
       </c>
       <c r="C140" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D140" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E140" s="6">
         <v>3</v>
@@ -5487,16 +5484,16 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B141" t="s">
         <v>30</v>
       </c>
       <c r="C141" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D141" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E141" s="6">
         <v>3</v>
@@ -5507,16 +5504,16 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B142" t="s">
         <v>30</v>
       </c>
       <c r="C142" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D142" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E142" s="6">
         <v>3</v>
@@ -5527,16 +5524,16 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B143" t="s">
         <v>30</v>
       </c>
       <c r="C143" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D143" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E143" s="6">
         <v>3</v>
@@ -5547,16 +5544,16 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B144" t="s">
         <v>30</v>
       </c>
       <c r="C144" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D144" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E144" s="6">
         <v>3</v>
@@ -5567,16 +5564,16 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B145" t="s">
         <v>31</v>
       </c>
       <c r="C145" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D145" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E145" s="6">
         <v>3</v>
@@ -5587,16 +5584,16 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B146" t="s">
         <v>31</v>
       </c>
       <c r="C146" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D146" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E146" s="6">
         <v>3</v>
@@ -5607,16 +5604,16 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B147" t="s">
         <v>31</v>
       </c>
       <c r="C147" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D147" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E147" s="6">
         <v>3</v>
@@ -5627,16 +5624,16 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B148" t="s">
         <v>31</v>
       </c>
       <c r="C148" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D148" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E148" s="6">
         <v>3</v>
@@ -5647,16 +5644,16 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B149" t="s">
         <v>31</v>
       </c>
       <c r="C149" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D149" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E149" s="6">
         <v>3</v>
@@ -5667,16 +5664,16 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B150" t="s">
         <v>31</v>
       </c>
       <c r="C150" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D150" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E150" s="6">
         <v>2</v>
@@ -5687,16 +5684,16 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B151" t="s">
         <v>31</v>
       </c>
       <c r="C151" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D151" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E151" s="6">
         <v>2</v>
@@ -5707,16 +5704,16 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B152" t="s">
         <v>31</v>
       </c>
       <c r="C152" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D152" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E152" s="6">
         <v>2</v>
@@ -5727,16 +5724,16 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B153" t="s">
         <v>32</v>
       </c>
       <c r="C153" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D153" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E153" s="6">
         <v>3</v>
@@ -5747,16 +5744,16 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B154" t="s">
         <v>32</v>
       </c>
       <c r="C154" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D154" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E154" s="6">
         <v>3</v>
@@ -5767,16 +5764,16 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B155" t="s">
         <v>32</v>
       </c>
       <c r="C155" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D155" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E155" s="6">
         <v>3</v>
@@ -5787,16 +5784,16 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B156" t="s">
         <v>32</v>
       </c>
       <c r="C156" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D156" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E156" s="6">
         <v>3</v>
@@ -5807,16 +5804,16 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B157" t="s">
         <v>32</v>
       </c>
       <c r="C157" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D157" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E157" s="6">
         <v>3</v>
@@ -5827,16 +5824,16 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B158" t="s">
         <v>32</v>
       </c>
       <c r="C158" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D158" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E158" s="6">
         <v>3</v>
@@ -5847,16 +5844,16 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B159" t="s">
         <v>32</v>
       </c>
       <c r="C159" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D159" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E159" s="6">
         <v>3</v>
@@ -5867,16 +5864,16 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B160" t="s">
         <v>33</v>
       </c>
       <c r="C160" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D160" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E160" s="6">
         <v>3</v>
@@ -5887,16 +5884,16 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B161" t="s">
         <v>33</v>
       </c>
       <c r="C161" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D161" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E161" s="6">
         <v>3</v>
@@ -5907,16 +5904,16 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B162" t="s">
         <v>33</v>
       </c>
       <c r="C162" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D162" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E162" s="6">
         <v>3</v>
@@ -5927,16 +5924,16 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B163" t="s">
         <v>33</v>
       </c>
       <c r="C163" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D163" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E163" s="6">
         <v>3</v>
@@ -5947,16 +5944,16 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B164" t="s">
         <v>33</v>
       </c>
       <c r="C164" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D164" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E164" s="6">
         <v>3</v>
@@ -5967,16 +5964,16 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B165" t="s">
         <v>33</v>
       </c>
       <c r="C165" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D165" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E165" s="6">
         <v>3</v>
@@ -5987,16 +5984,16 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B166" t="s">
         <v>33</v>
       </c>
       <c r="C166" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D166" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E166" s="6">
         <v>3</v>
@@ -6007,16 +6004,16 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B167" t="s">
         <v>34</v>
       </c>
       <c r="C167" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D167" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E167" s="6">
         <v>4</v>
@@ -6027,16 +6024,16 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B168" t="s">
         <v>34</v>
       </c>
       <c r="C168" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D168" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E168" s="6">
         <v>4</v>
@@ -6047,16 +6044,16 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B169" t="s">
         <v>34</v>
       </c>
       <c r="C169" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D169" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E169" s="6">
         <v>4</v>
@@ -6067,16 +6064,16 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B170" t="s">
         <v>34</v>
       </c>
       <c r="C170" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D170" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E170" s="6">
         <v>4</v>
@@ -6087,16 +6084,16 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B171" t="s">
         <v>34</v>
       </c>
       <c r="C171" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D171" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E171" s="6">
         <v>4</v>
@@ -6107,216 +6104,216 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B172" t="s">
         <v>35</v>
       </c>
       <c r="C172" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D172" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E172" s="6">
         <v>5</v>
       </c>
       <c r="F172" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B173" t="s">
         <v>35</v>
       </c>
       <c r="C173" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D173" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E173" s="6">
         <v>5</v>
       </c>
       <c r="F173" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B174" t="s">
         <v>35</v>
       </c>
       <c r="C174" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D174" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E174" s="6">
         <v>5</v>
       </c>
       <c r="F174" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B175" t="s">
         <v>35</v>
       </c>
       <c r="C175" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D175" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E175" s="6">
         <v>5</v>
       </c>
       <c r="F175" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B176" t="s">
         <v>35</v>
       </c>
       <c r="C176" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D176" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E176" s="6">
         <v>5</v>
       </c>
       <c r="F176" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B177" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C177" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D177" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E177" s="6">
         <v>6</v>
       </c>
       <c r="F177" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B178" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C178" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D178" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E178" s="6">
         <v>6</v>
       </c>
       <c r="F178" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B179" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C179" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D179" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E179" s="6">
         <v>6</v>
       </c>
       <c r="F179" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B180" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C180" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D180" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E180" s="6">
         <v>6</v>
       </c>
       <c r="F180" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B181" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C181" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D181" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E181" s="6">
         <v>6</v>
       </c>
       <c r="F181" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B182" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C182" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D182" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E182" s="6">
         <v>3</v>
@@ -6327,16 +6324,16 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B183" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C183" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D183" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E183" s="6">
         <v>3</v>
@@ -6347,16 +6344,16 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B184" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C184" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D184" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E184" s="6">
         <v>4</v>
@@ -6367,16 +6364,16 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B185" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C185" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D185" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E185" s="6">
         <v>4</v>
@@ -6387,16 +6384,16 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B186" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C186" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D186" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E186" s="6">
         <v>4</v>
@@ -6407,16 +6404,16 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B187" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C187" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D187" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E187" s="6">
         <v>4</v>
@@ -6427,16 +6424,16 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B188" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C188" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D188" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E188" s="6">
         <v>4</v>
@@ -6447,16 +6444,16 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B189" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C189" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D189" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E189" s="6">
         <v>4</v>
@@ -6467,16 +6464,16 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B190" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C190" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D190" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E190" s="6">
         <v>4</v>
@@ -6505,22 +6502,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -6540,7 +6537,7 @@
         <v>20</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -6560,7 +6557,7 @@
         <v>20</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -6580,7 +6577,7 @@
         <v>40</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -6600,7 +6597,7 @@
         <v>40</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -6618,7 +6615,7 @@
         <v>20</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -6638,7 +6635,7 @@
         <v>40</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -6658,7 +6655,7 @@
         <v>40</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -6678,7 +6675,7 @@
         <v>40</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -6695,7 +6692,7 @@
         <v>40</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -6715,7 +6712,7 @@
         <v>40</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -6735,7 +6732,7 @@
         <v>40</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -6755,7 +6752,7 @@
         <v>40</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -6775,7 +6772,7 @@
         <v>20</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -6795,7 +6792,7 @@
         <v>40</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -6815,7 +6812,7 @@
         <v>40</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -6835,7 +6832,7 @@
         <v>40</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -6853,7 +6850,7 @@
         <v>20</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -6873,7 +6870,7 @@
         <v>40</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -6893,7 +6890,7 @@
         <v>40</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -6913,7 +6910,7 @@
         <v>40</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -6930,7 +6927,7 @@
         <v>40</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -6950,7 +6947,7 @@
         <v>40</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -6970,7 +6967,7 @@
         <v>40</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -6990,7 +6987,7 @@
         <v>40</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -7010,7 +7007,7 @@
         <v>20</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -7030,7 +7027,7 @@
         <v>40</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -7050,7 +7047,7 @@
         <v>40</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -7070,7 +7067,7 @@
         <v>40</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -7088,7 +7085,7 @@
         <v>20</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -7108,7 +7105,7 @@
         <v>40</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -7128,7 +7125,7 @@
         <v>40</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -7148,7 +7145,7 @@
         <v>40</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -7165,7 +7162,7 @@
         <v>40</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -7185,7 +7182,7 @@
         <v>40</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -7205,7 +7202,7 @@
         <v>40</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -7225,7 +7222,7 @@
         <v>40</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -7245,7 +7242,7 @@
         <v>20</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -7265,7 +7262,7 @@
         <v>40</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -7285,7 +7282,7 @@
         <v>40</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -7305,7 +7302,7 @@
         <v>40</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -7323,7 +7320,7 @@
         <v>20</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -7343,7 +7340,7 @@
         <v>40</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -7363,7 +7360,7 @@
         <v>40</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -7383,7 +7380,7 @@
         <v>40</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -7400,7 +7397,7 @@
         <v>40</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -7420,7 +7417,7 @@
         <v>40</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -7440,7 +7437,7 @@
         <v>40</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -7460,7 +7457,7 @@
         <v>40</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -7480,7 +7477,7 @@
         <v>40</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -7500,7 +7497,7 @@
         <v>30</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -7520,7 +7517,7 @@
         <v>30</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -7540,7 +7537,7 @@
         <v>30</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -7558,7 +7555,7 @@
         <v>20</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -7578,7 +7575,7 @@
         <v>30</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -7598,7 +7595,7 @@
         <v>30</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -7618,7 +7615,7 @@
         <v>30</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/data/database_scheduler.xlsx
+++ b/data/database_scheduler.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mersi\BZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31ADEC0D-6820-4D82-A93E-8806A4537D7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6948E0E-FC95-4478-9864-205BED74CB8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
   </bookViews>
   <sheets>
     <sheet name="Guru" sheetId="2" r:id="rId1"/>
     <sheet name="Mapel" sheetId="3" r:id="rId2"/>
     <sheet name="Rombel" sheetId="7" r:id="rId3"/>
-    <sheet name="Guru_Mengajar" sheetId="8" r:id="rId4"/>
-    <sheet name="Hari_Jam" sheetId="9" r:id="rId5"/>
+    <sheet name="Mengajar" sheetId="8" r:id="rId4"/>
+    <sheet name="Slot" sheetId="9" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>

--- a/data/database_scheduler.xlsx
+++ b/data/database_scheduler.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mersi\BZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6948E0E-FC95-4478-9864-205BED74CB8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31ADEC0D-6820-4D82-A93E-8806A4537D7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
   </bookViews>
   <sheets>
     <sheet name="Guru" sheetId="2" r:id="rId1"/>
     <sheet name="Mapel" sheetId="3" r:id="rId2"/>
     <sheet name="Rombel" sheetId="7" r:id="rId3"/>
-    <sheet name="Mengajar" sheetId="8" r:id="rId4"/>
-    <sheet name="Slot" sheetId="9" r:id="rId5"/>
+    <sheet name="Guru_Mengajar" sheetId="8" r:id="rId4"/>
+    <sheet name="Hari_Jam" sheetId="9" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>

--- a/data/database_scheduler.xlsx
+++ b/data/database_scheduler.xlsx
@@ -8,23 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mersi\BZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31ADEC0D-6820-4D82-A93E-8806A4537D7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{902BFB60-255C-4A3A-884F-C2F8FD18838F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
   </bookViews>
   <sheets>
     <sheet name="Guru" sheetId="2" r:id="rId1"/>
     <sheet name="Mapel" sheetId="3" r:id="rId2"/>
     <sheet name="Rombel" sheetId="7" r:id="rId3"/>
-    <sheet name="Guru_Mengajar" sheetId="8" r:id="rId4"/>
-    <sheet name="Hari_Jam" sheetId="9" r:id="rId5"/>
+    <sheet name="Mengajar" sheetId="8" r:id="rId4"/>
+    <sheet name="Slot" sheetId="9" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="156">
   <si>
     <t>Nama Guru</t>
   </si>
@@ -485,19 +485,10 @@
     <t>Shift</t>
   </si>
   <si>
-    <t>2+2</t>
-  </si>
-  <si>
     <t>PAGI</t>
   </si>
   <si>
-    <t>2+1</t>
-  </si>
-  <si>
     <t>SIANG</t>
-  </si>
-  <si>
-    <t>2+2+1</t>
   </si>
   <si>
     <t>Milenia, S.Pd.</t>
@@ -1761,7 +1752,7 @@
         <v>4</v>
       </c>
       <c r="E23" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -1778,7 +1769,7 @@
         <v>2</v>
       </c>
       <c r="E24" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -1795,7 +1786,7 @@
         <v>2</v>
       </c>
       <c r="E25" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -1922,7 +1913,7 @@
         <v>74</v>
       </c>
       <c r="B33" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>77</v>
@@ -2041,7 +2032,7 @@
         <v>3</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -2064,10 +2055,10 @@
         <v>6</v>
       </c>
       <c r="G3" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2090,10 +2081,10 @@
         <v>6</v>
       </c>
       <c r="G4" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -2116,10 +2107,10 @@
         <v>6</v>
       </c>
       <c r="G5" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -2141,11 +2132,11 @@
       <c r="F6" s="1">
         <v>9</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>155</v>
+      <c r="G6" s="1">
+        <v>2.1</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -2168,10 +2159,10 @@
         <v>6</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -2193,11 +2184,11 @@
       <c r="F8" s="1">
         <v>6</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -2220,10 +2211,10 @@
         <v>4</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -2246,10 +2237,10 @@
         <v>2</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -2275,7 +2266,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -2301,7 +2292,7 @@
         <v>3</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -2327,7 +2318,7 @@
         <v>3</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -2353,7 +2344,7 @@
         <v>3</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -2379,7 +2370,7 @@
         <v>3</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -2405,7 +2396,7 @@
         <v>2</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -2428,10 +2419,10 @@
         <v>9</v>
       </c>
       <c r="G17" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -6207,7 +6198,7 @@
         <v>74</v>
       </c>
       <c r="B177" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C177" t="s">
         <v>84</v>
@@ -6227,7 +6218,7 @@
         <v>74</v>
       </c>
       <c r="B178" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C178" t="s">
         <v>84</v>
@@ -6247,7 +6238,7 @@
         <v>74</v>
       </c>
       <c r="B179" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C179" t="s">
         <v>84</v>
@@ -6267,7 +6258,7 @@
         <v>74</v>
       </c>
       <c r="B180" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C180" t="s">
         <v>84</v>
@@ -6287,7 +6278,7 @@
         <v>74</v>
       </c>
       <c r="B181" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C181" t="s">
         <v>84</v>

--- a/data/database_scheduler.xlsx
+++ b/data/database_scheduler.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mersi\BZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{902BFB60-255C-4A3A-884F-C2F8FD18838F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{348547BC-A3C8-454E-8B07-AFAA42DD2007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
+    <workbookView xWindow="390" yWindow="30" windowWidth="19560" windowHeight="10890" activeTab="3" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
   </bookViews>
   <sheets>
     <sheet name="Guru" sheetId="2" r:id="rId1"/>
     <sheet name="Mapel" sheetId="3" r:id="rId2"/>
     <sheet name="Rombel" sheetId="7" r:id="rId3"/>
-    <sheet name="Mengajar" sheetId="8" r:id="rId4"/>
+    <sheet name="Guru_Mengajar" sheetId="8" r:id="rId4"/>
     <sheet name="Slot" sheetId="9" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>

--- a/data/database_scheduler.xlsx
+++ b/data/database_scheduler.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mersi\BZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{348547BC-A3C8-454E-8B07-AFAA42DD2007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A0901D0-9C08-4043-AA96-1DB4FBC5457D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="30" windowWidth="19560" windowHeight="10890" activeTab="3" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
+    <workbookView xWindow="390" yWindow="30" windowWidth="19560" windowHeight="10890" activeTab="4" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
   </bookViews>
   <sheets>
     <sheet name="Guru" sheetId="2" r:id="rId1"/>
     <sheet name="Mapel" sheetId="3" r:id="rId2"/>
     <sheet name="Rombel" sheetId="7" r:id="rId3"/>
     <sheet name="Guru_Mengajar" sheetId="8" r:id="rId4"/>
-    <sheet name="Slot" sheetId="9" r:id="rId5"/>
+    <sheet name="Hari_Jam" sheetId="9" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>

--- a/data/database_scheduler.xlsx
+++ b/data/database_scheduler.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mersi\BZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A0901D0-9C08-4043-AA96-1DB4FBC5457D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11A9EF38-EE1E-4652-9B3D-AC105D528A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="30" windowWidth="19560" windowHeight="10890" activeTab="4" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
+    <workbookView xWindow="390" yWindow="30" windowWidth="19560" windowHeight="10890" activeTab="3" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
   </bookViews>
   <sheets>
     <sheet name="Guru" sheetId="2" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Guru_Mengajar" sheetId="8" r:id="rId4"/>
     <sheet name="Hari_Jam" sheetId="9" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
@@ -422,9 +422,6 @@
     <t>Mapel</t>
   </si>
   <si>
-    <t>Pembagian</t>
-  </si>
-  <si>
     <t>2,2,1</t>
   </si>
   <si>
@@ -492,6 +489,9 @@
   </si>
   <si>
     <t>Milenia, S.Pd.</t>
+  </si>
+  <si>
+    <t>Slot</t>
   </si>
 </sst>
 </file>
@@ -1814,7 +1814,7 @@
         <v>31</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D27" t="s">
         <v>20</v>
@@ -1831,7 +1831,7 @@
         <v>31</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D28" t="s">
         <v>6</v>
@@ -1848,7 +1848,7 @@
         <v>32</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D29" t="s">
         <v>4</v>
@@ -1865,7 +1865,7 @@
         <v>33</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D30" t="s">
         <v>8</v>
@@ -1882,7 +1882,7 @@
         <v>34</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D31" t="s">
         <v>6</v>
@@ -1913,7 +1913,7 @@
         <v>74</v>
       </c>
       <c r="B33" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>77</v>
@@ -1997,16 +1997,16 @@
         <v>41</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -2032,7 +2032,7 @@
         <v>3</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -2046,19 +2046,19 @@
         <v>0</v>
       </c>
       <c r="D3" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2072,19 +2072,19 @@
         <v>0</v>
       </c>
       <c r="D4" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F4" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -2098,19 +2098,19 @@
         <v>0</v>
       </c>
       <c r="D5" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F5" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -2136,7 +2136,7 @@
         <v>2.1</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -2159,10 +2159,10 @@
         <v>6</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -2188,7 +2188,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -2211,10 +2211,10 @@
         <v>4</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -2237,10 +2237,10 @@
         <v>2</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -2266,7 +2266,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -2292,7 +2292,7 @@
         <v>3</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -2318,7 +2318,7 @@
         <v>3</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -2344,7 +2344,7 @@
         <v>3</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -2370,7 +2370,7 @@
         <v>3</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -2396,7 +2396,7 @@
         <v>2</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -2410,19 +2410,19 @@
         <v>0</v>
       </c>
       <c r="D17" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E17" s="6">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F17" s="6">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G17" s="6">
         <v>0</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -2683,7 +2683,7 @@
         <v>80</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="G1" s="2"/>
     </row>
@@ -2704,7 +2704,7 @@
         <v>5</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G2" s="3"/>
     </row>
@@ -2725,7 +2725,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G3" s="3"/>
     </row>
@@ -2746,7 +2746,7 @@
         <v>5</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G4" s="3"/>
     </row>
@@ -2767,7 +2767,7 @@
         <v>5</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G5" s="3"/>
     </row>
@@ -2788,7 +2788,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G6" s="3"/>
     </row>
@@ -2797,7 +2797,7 @@
         <v>44</v>
       </c>
       <c r="B7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C7" t="s">
         <v>101</v>
@@ -2818,7 +2818,7 @@
         <v>44</v>
       </c>
       <c r="B8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C8" t="s">
         <v>101</v>
@@ -2838,7 +2838,7 @@
         <v>44</v>
       </c>
       <c r="B9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C9" t="s">
         <v>101</v>
@@ -2858,7 +2858,7 @@
         <v>44</v>
       </c>
       <c r="B10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C10" t="s">
         <v>101</v>
@@ -2878,7 +2878,7 @@
         <v>44</v>
       </c>
       <c r="B11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C11" t="s">
         <v>101</v>
@@ -3010,7 +3010,7 @@
         <v>5</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -3030,7 +3030,7 @@
         <v>5</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -3050,7 +3050,7 @@
         <v>5</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -3070,7 +3070,7 @@
         <v>5</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -3090,7 +3090,7 @@
         <v>5</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -3870,7 +3870,7 @@
         <v>6</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -3890,7 +3890,7 @@
         <v>6</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -3910,7 +3910,7 @@
         <v>6</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -3930,7 +3930,7 @@
         <v>6</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -3950,7 +3950,7 @@
         <v>6</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -4170,7 +4170,7 @@
         <v>6</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -4190,7 +4190,7 @@
         <v>6</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -4210,7 +4210,7 @@
         <v>6</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -4230,7 +4230,7 @@
         <v>6</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -4250,7 +4250,7 @@
         <v>6</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -4790,7 +4790,7 @@
         <v>5</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -4810,7 +4810,7 @@
         <v>5</v>
       </c>
       <c r="F107" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -4830,7 +4830,7 @@
         <v>5</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -4850,7 +4850,7 @@
         <v>5</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -4870,7 +4870,7 @@
         <v>5</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -4890,7 +4890,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -4910,7 +4910,7 @@
         <v>5</v>
       </c>
       <c r="F112" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -4930,7 +4930,7 @@
         <v>5</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -4950,7 +4950,7 @@
         <v>5</v>
       </c>
       <c r="F114" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -4970,7 +4970,7 @@
         <v>5</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -4990,7 +4990,7 @@
         <v>5</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -5010,7 +5010,7 @@
         <v>5</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -5030,7 +5030,7 @@
         <v>5</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -5050,7 +5050,7 @@
         <v>5</v>
       </c>
       <c r="F119" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -5070,7 +5070,7 @@
         <v>5</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -5361,7 +5361,7 @@
         <v>29</v>
       </c>
       <c r="C135" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D135" t="s">
         <v>116</v>
@@ -5381,7 +5381,7 @@
         <v>29</v>
       </c>
       <c r="C136" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D136" t="s">
         <v>118</v>
@@ -5401,7 +5401,7 @@
         <v>29</v>
       </c>
       <c r="C137" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D137" t="s">
         <v>119</v>
@@ -6110,7 +6110,7 @@
         <v>5</v>
       </c>
       <c r="F172" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -6130,7 +6130,7 @@
         <v>5</v>
       </c>
       <c r="F173" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -6150,7 +6150,7 @@
         <v>5</v>
       </c>
       <c r="F174" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -6170,7 +6170,7 @@
         <v>5</v>
       </c>
       <c r="F175" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -6190,7 +6190,7 @@
         <v>5</v>
       </c>
       <c r="F176" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -6198,7 +6198,7 @@
         <v>74</v>
       </c>
       <c r="B177" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C177" t="s">
         <v>84</v>
@@ -6210,7 +6210,7 @@
         <v>6</v>
       </c>
       <c r="F177" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -6218,7 +6218,7 @@
         <v>74</v>
       </c>
       <c r="B178" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C178" t="s">
         <v>84</v>
@@ -6230,7 +6230,7 @@
         <v>6</v>
       </c>
       <c r="F178" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -6238,7 +6238,7 @@
         <v>74</v>
       </c>
       <c r="B179" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C179" t="s">
         <v>84</v>
@@ -6250,7 +6250,7 @@
         <v>6</v>
       </c>
       <c r="F179" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -6258,7 +6258,7 @@
         <v>74</v>
       </c>
       <c r="B180" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C180" t="s">
         <v>84</v>
@@ -6270,7 +6270,7 @@
         <v>6</v>
       </c>
       <c r="F180" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -6278,7 +6278,7 @@
         <v>74</v>
       </c>
       <c r="B181" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C181" t="s">
         <v>84</v>
@@ -6290,7 +6290,7 @@
         <v>6</v>
       </c>
       <c r="F181" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -6493,22 +6493,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -6528,7 +6528,7 @@
         <v>20</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -6548,7 +6548,7 @@
         <v>20</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -6568,7 +6568,7 @@
         <v>40</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -6588,7 +6588,7 @@
         <v>40</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -6606,7 +6606,7 @@
         <v>20</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -6626,7 +6626,7 @@
         <v>40</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -6646,7 +6646,7 @@
         <v>40</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -6666,7 +6666,7 @@
         <v>40</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -6683,7 +6683,7 @@
         <v>40</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -6703,7 +6703,7 @@
         <v>40</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -6723,7 +6723,7 @@
         <v>40</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -6743,7 +6743,7 @@
         <v>40</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -6763,7 +6763,7 @@
         <v>20</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -6783,7 +6783,7 @@
         <v>40</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -6803,7 +6803,7 @@
         <v>40</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -6823,7 +6823,7 @@
         <v>40</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -6841,7 +6841,7 @@
         <v>20</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -6861,7 +6861,7 @@
         <v>40</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -6881,7 +6881,7 @@
         <v>40</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -6901,7 +6901,7 @@
         <v>40</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -6918,7 +6918,7 @@
         <v>40</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -6938,7 +6938,7 @@
         <v>40</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -6958,7 +6958,7 @@
         <v>40</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -6978,7 +6978,7 @@
         <v>40</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -6998,7 +6998,7 @@
         <v>20</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -7018,7 +7018,7 @@
         <v>40</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -7038,7 +7038,7 @@
         <v>40</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -7058,7 +7058,7 @@
         <v>40</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -7076,7 +7076,7 @@
         <v>20</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -7096,7 +7096,7 @@
         <v>40</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -7116,7 +7116,7 @@
         <v>40</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -7136,7 +7136,7 @@
         <v>40</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -7153,7 +7153,7 @@
         <v>40</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -7173,7 +7173,7 @@
         <v>40</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -7193,7 +7193,7 @@
         <v>40</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -7213,7 +7213,7 @@
         <v>40</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -7233,7 +7233,7 @@
         <v>20</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -7253,7 +7253,7 @@
         <v>40</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -7273,7 +7273,7 @@
         <v>40</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -7293,7 +7293,7 @@
         <v>40</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -7311,7 +7311,7 @@
         <v>20</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -7331,7 +7331,7 @@
         <v>40</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -7351,7 +7351,7 @@
         <v>40</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -7371,7 +7371,7 @@
         <v>40</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -7388,7 +7388,7 @@
         <v>40</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -7408,7 +7408,7 @@
         <v>40</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -7428,7 +7428,7 @@
         <v>40</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -7448,7 +7448,7 @@
         <v>40</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -7468,7 +7468,7 @@
         <v>40</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -7488,7 +7488,7 @@
         <v>30</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -7508,7 +7508,7 @@
         <v>30</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -7528,7 +7528,7 @@
         <v>30</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -7546,7 +7546,7 @@
         <v>20</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -7566,7 +7566,7 @@
         <v>30</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -7586,7 +7586,7 @@
         <v>30</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -7606,7 +7606,7 @@
         <v>30</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/data/database_scheduler.xlsx
+++ b/data/database_scheduler.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mersi\BZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11A9EF38-EE1E-4652-9B3D-AC105D528A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D470BEBD-6AFB-4DDE-A879-B80423AE8320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="30" windowWidth="19560" windowHeight="10890" activeTab="3" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
+    <workbookView xWindow="10245" yWindow="0" windowWidth="10245" windowHeight="10920" activeTab="1" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
   </bookViews>
   <sheets>
     <sheet name="Guru" sheetId="2" r:id="rId1"/>
     <sheet name="Mapel" sheetId="3" r:id="rId2"/>
     <sheet name="Rombel" sheetId="7" r:id="rId3"/>
     <sheet name="Guru_Mengajar" sheetId="8" r:id="rId4"/>
-    <sheet name="Hari_Jam" sheetId="9" r:id="rId5"/>
+    <sheet name="Slot" sheetId="9" r:id="rId5"/>
   </sheets>
   <calcPr calcId="181029"/>
 </workbook>
@@ -2170,7 +2170,7 @@
         <v>90</v>
       </c>
       <c r="B8" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="C8" s="1">
         <v>4</v>
@@ -2196,7 +2196,7 @@
         <v>91</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="C9" s="1">
         <v>5</v>
@@ -2222,7 +2222,7 @@
         <v>92</v>
       </c>
       <c r="B10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C10" s="1">
         <v>5</v>
@@ -2248,7 +2248,7 @@
         <v>93</v>
       </c>
       <c r="B11" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C11" s="1">
         <v>4</v>
@@ -2300,7 +2300,7 @@
         <v>95</v>
       </c>
       <c r="B13" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="C13" s="1">
         <v>3</v>
@@ -2326,7 +2326,7 @@
         <v>96</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="C14" s="1">
         <v>3</v>
@@ -2655,7 +2655,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E6B6589-81EB-464C-9D2E-94A0AC6F84FB}">
-  <dimension ref="A1:G190"/>
+  <dimension ref="A1:G191"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.5703125" customWidth="1"/>
@@ -6471,6 +6471,12 @@
       </c>
       <c r="F190" s="6">
         <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E191" s="6">
+        <f>SUM(E2:E190)</f>
+        <v>615</v>
       </c>
     </row>
   </sheetData>
